--- a/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">

--- a/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
@@ -3322,7 +3322,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G8">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>c, d, b, a</t>
+          <t>e, b, d, f</t>
         </is>
       </c>
       <c r="G12">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G32">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seasonal naive: October Rs 427.6 lakh and November Rs 297.0 lakh, which puts the spike in October. Festival-aligned for November, Diwali's month in 2026: October 2025's Rs 427.6 lakh times 1.04, about Rs 444.7 lakh. The spike belongs in November.</t>
+          <t>Seasonal naive: October Rs 427.6 lakh and November Rs 297.0 lakh, which puts the spike in October. Festival-aligned: November, Diwali's month in 2026, gets October 2025's Rs 427.6 lakh times 1.04, about Rs 444.7 lakh, and October gets November 2025's Rs 297.0 lakh times 1.04, about Rs 308.9 lakh. The spike belongs in November.</t>
         </is>
       </c>
       <c r="G34">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G43">

--- a/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G10">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G18">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W04/SAT/answer-key/C2_W04_SAT_item_analysis_TRAINER.xlsx
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
